--- a/bin/Debug/Logs/202508/Log_20250801-090757.xlsx
+++ b/bin/Debug/Logs/202508/Log_20250801-090757.xlsx
@@ -11,44 +11,6 @@
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
 </x:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>日志时间</x:t>
-  </x:si>
-  <x:si>
-    <x:t>日志等级</x:t>
-  </x:si>
-  <x:si>
-    <x:t>日志类型</x:t>
-  </x:si>
-  <x:si>
-    <x:t>日志内容</x:t>
-  </x:si>
-  <x:si>
-    <x:t>debug</x:t>
-  </x:si>
-  <x:si>
-    <x:t>run</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GTN_Open(5,1):(-6)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[error][2025-08-01 09:07:56]：InitCard() System.Exception: 执行指令:  GT_Open
-打开控制器失败(-6)
-   在 H5509_V2.Motion.ErrorHandler(String command, Int16 error) 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 46
-   在 H5509_V2.Motion.InitCard() 位置 D:\GitHub\H5509_V2\动作\Motion.cs:行号 59</x:t>
-  </x:si>
-  <x:si>
-    <x:t>创建新文件: D:\GitHub\H5509_V2\bin\Debug\Logs\202508\Log_20250801-090757.xlsx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>[Code]1400448,[Msg]温控器连接失败!</x:t>
-  </x:si>
-</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -481,6 +443,790 @@
         <x:v>9</x:v>
       </x:c>
     </x:row>
+    <x:row r="6" spans="1:4">
+      <x:c r="A6" s="1">
+        <x:v>45870.4252600116</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:4">
+      <x:c r="A7" s="1">
+        <x:v>45870.4252603357</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:4">
+      <x:c r="A8" s="1">
+        <x:v>45870.4253939583</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:4">
+      <x:c r="A9" s="1">
+        <x:v>45870.4280177662</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:4">
+      <x:c r="A10" s="1">
+        <x:v>45870.4280179398</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:4">
+      <x:c r="A11" s="1">
+        <x:v>45870.4281471644</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:4">
+      <x:c r="A12" s="1">
+        <x:v>45870.4299995833</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:4">
+      <x:c r="A13" s="1">
+        <x:v>45870.4299997685</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:4">
+      <x:c r="A14" s="1">
+        <x:v>45870.4300650694</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:4">
+      <x:c r="A15" s="1">
+        <x:v>45870.430125081</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:4">
+      <x:c r="A16" s="1">
+        <x:v>45870.4317056481</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:4">
+      <x:c r="A17" s="1">
+        <x:v>45870.4317058333</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:4">
+      <x:c r="A18" s="1">
+        <x:v>45870.4318313542</x:v>
+      </x:c>
+      <x:c r="B18" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C18" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:4">
+      <x:c r="A19" s="1">
+        <x:v>45870.4682503125</x:v>
+      </x:c>
+      <x:c r="B19" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C19" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:4">
+      <x:c r="A20" s="1">
+        <x:v>45870.4682504861</x:v>
+      </x:c>
+      <x:c r="B20" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C20" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:4">
+      <x:c r="A21" s="1">
+        <x:v>45870.4683748495</x:v>
+      </x:c>
+      <x:c r="B21" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C21" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D21" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:4">
+      <x:c r="A22" s="1">
+        <x:v>45870.4725410648</x:v>
+      </x:c>
+      <x:c r="B22" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C22" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D22" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:4">
+      <x:c r="A23" s="1">
+        <x:v>45870.4734147454</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:4">
+      <x:c r="A24" s="1">
+        <x:v>45870.4734149074</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:4">
+      <x:c r="A25" s="1">
+        <x:v>45870.4735435995</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:4">
+      <x:c r="A26" s="1">
+        <x:v>45870.4785304514</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:4">
+      <x:c r="A27" s="1">
+        <x:v>45870.4785306481</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D27" s="2" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:4">
+      <x:c r="A28" s="1">
+        <x:v>45870.4786654861</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:4">
+      <x:c r="A29" s="1">
+        <x:v>45870.4793303241</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30" s="1">
+        <x:v>45870.4793304977</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D30" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:4">
+      <x:c r="A31" s="1">
+        <x:v>45870.4794652431</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:4">
+      <x:c r="A32" s="1">
+        <x:v>45870.4800196065</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:4">
+      <x:c r="A33" s="1">
+        <x:v>45870.4823558912</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:4">
+      <x:c r="A34" s="1">
+        <x:v>45870.4823560532</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D34" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:4">
+      <x:c r="A35" s="1">
+        <x:v>45870.4824824074</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:4">
+      <x:c r="A36" s="1">
+        <x:v>45870.4827188194</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:4">
+      <x:c r="A37" s="1">
+        <x:v>45870.4830246875</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:4">
+      <x:c r="A38" s="1">
+        <x:v>45870.4830847222</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:4">
+      <x:c r="A39" s="1">
+        <x:v>45870.4830847338</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:4">
+      <x:c r="A40" s="1">
+        <x:v>45870.4834407986</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:4">
+      <x:c r="A41" s="1">
+        <x:v>45870.4835006713</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:4">
+      <x:c r="A42" s="1">
+        <x:v>45870.4835006829</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:4">
+      <x:c r="A43" s="1">
+        <x:v>45870.4837006944</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:4">
+      <x:c r="A44" s="1">
+        <x:v>45870.48373625</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:4">
+      <x:c r="A45" s="1">
+        <x:v>45870.4838306597</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:4">
+      <x:c r="A46" s="1">
+        <x:v>45870.4838306713</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:4">
+      <x:c r="A47" s="1">
+        <x:v>45870.6307898032</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:4">
+      <x:c r="A48" s="1">
+        <x:v>45870.6307899769</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D48" s="2" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:4">
+      <x:c r="A49" s="1">
+        <x:v>45870.6309187384</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:4">
+      <x:c r="A50" s="1">
+        <x:v>45870.8001759028</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:4">
+      <x:c r="A51" s="1">
+        <x:v>45870.8001760764</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D51" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:4">
+      <x:c r="A52" s="1">
+        <x:v>45870.8003003588</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:4">
+      <x:c r="A53" s="1">
+        <x:v>45870.912273125</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:4">
+      <x:c r="A54" s="1">
+        <x:v>45870.9122733565</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D54" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:4">
+      <x:c r="A55" s="1">
+        <x:v>45870.9169521296</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:4">
+      <x:c r="A56" s="1">
+        <x:v>45870.9169523032</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D56" s="2" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:4">
+      <x:c r="A57" s="1">
+        <x:v>45870.9170985069</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:4">
+      <x:c r="A58" s="1">
+        <x:v>45870.9176322685</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:4">
+      <x:c r="A59" s="1">
+        <x:v>45870.9189084838</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:4">
+      <x:c r="A60" s="1">
+        <x:v>45870.9189086806</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D60" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:4">
+      <x:c r="A61" s="1">
+        <x:v>45870.9190487153</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
